--- a/data/trans_orig/P16A13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485230</t>
+          <t>485630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>450676</t>
+          <t>450969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>462893</t>
+          <t>463546</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>941243</t>
+          <t>942514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>955983</t>
+          <t>956138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>20693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29172</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>714946</t>
+          <t>714796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>729218</t>
+          <t>728888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>611329</t>
+          <t>610479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622560</t>
+          <t>622536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1331810</t>
+          <t>1330931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1348997</t>
+          <t>1349298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>18659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40071</t>
+          <t>38331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613153</t>
+          <t>612555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629077</t>
+          <t>629180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669296</t>
+          <t>667908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682740</t>
+          <t>682655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1287323</t>
+          <t>1289063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1309260</t>
+          <t>1308735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47492</t>
+          <t>47646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>496225</t>
+          <t>496463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511515</t>
+          <t>511966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484298</t>
+          <t>484995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502089</t>
+          <t>502522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>987297</t>
+          <t>987143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1010201</t>
+          <t>1010865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34700</t>
+          <t>34417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>27548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>51762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363503</t>
+          <t>363427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377864</t>
+          <t>378080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>369286</t>
+          <t>369569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>388593</t>
+          <t>388834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>737560</t>
+          <t>738934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>761840</t>
+          <t>763148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35740</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>51907</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271856</t>
+          <t>270955</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286382</t>
+          <t>285697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307194</t>
+          <t>306404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325184</t>
+          <t>325548</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>585232</t>
+          <t>583610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>607574</t>
+          <t>608183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>184337</t>
+          <t>185731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200102</t>
+          <t>200714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>299449</t>
+          <t>300032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>319130</t>
+          <t>319552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491052</t>
+          <t>491511</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>515907</t>
+          <t>516117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70617</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>106821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>101921</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>142806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178837</t>
+          <t>181139</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>234861</t>
+          <t>237608</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3166911</t>
+          <t>3168704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204908</t>
+          <t>3204949</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3236809</t>
+          <t>3236391</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3277276</t>
+          <t>3277638</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6419861</t>
+          <t>6417114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6475885</t>
+          <t>6473583</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438883</t>
+          <t>438561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450850</t>
+          <t>450423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420545</t>
+          <t>419508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428373</t>
+          <t>428359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863760</t>
+          <t>863167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>877696</t>
+          <t>877094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661859</t>
+          <t>661045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677726</t>
+          <t>677774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>587558</t>
+          <t>586746</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>602940</t>
+          <t>602464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1254185</t>
+          <t>1253306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1276876</t>
+          <t>1276551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>28175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54816</t>
+          <t>54773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650249</t>
+          <t>651879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669520</t>
+          <t>669612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>671993</t>
+          <t>671835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>691706</t>
+          <t>691899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1331173</t>
+          <t>1331216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1357479</t>
+          <t>1356952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47026</t>
+          <t>45144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>54086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88257</t>
+          <t>88909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>567591</t>
+          <t>569473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>593202</t>
+          <t>593638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>560006</t>
+          <t>561898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>587143</t>
+          <t>587460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1140432</t>
+          <t>1139780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1176606</t>
+          <t>1174603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46035</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62745</t>
+          <t>63008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>404214</t>
+          <t>405272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420135</t>
+          <t>419993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>401765</t>
+          <t>400986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425314</t>
+          <t>424652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813399</t>
+          <t>813136</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>840720</t>
+          <t>840953</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51427</t>
+          <t>51671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78212</t>
+          <t>78176</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270199</t>
+          <t>268785</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291149</t>
+          <t>291009</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302569</t>
+          <t>302325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325969</t>
+          <t>325749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>580216</t>
+          <t>580252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>611117</t>
+          <t>610484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45593</t>
+          <t>45728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30989</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>54140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93809</t>
+          <t>93248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203443</t>
+          <t>203308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226554</t>
+          <t>226783</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>329162</t>
+          <t>332613</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355764</t>
+          <t>356789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>541980</t>
+          <t>542541</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>578490</t>
+          <t>577257</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>114170</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166447</t>
+          <t>167490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163853</t>
+          <t>162886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220822</t>
+          <t>219087</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>295469</t>
+          <t>296390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>369878</t>
+          <t>368209</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3249378</t>
+          <t>3248335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3301655</t>
+          <t>3298543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3326288</t>
+          <t>3328023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3383257</t>
+          <t>3384224</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6593056</t>
+          <t>6594725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6667465</t>
+          <t>6666544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>408474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383635</t>
+          <t>384374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394048</t>
+          <t>394754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>798376</t>
+          <t>798213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>812220</t>
+          <t>812192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571687</t>
+          <t>571669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585579</t>
+          <t>585537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>546821</t>
+          <t>546762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>558990</t>
+          <t>558939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124396</t>
+          <t>1123863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1142932</t>
+          <t>1142077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>22602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35511</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647470</t>
+          <t>646495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662715</t>
+          <t>662150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641361</t>
+          <t>641993</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656080</t>
+          <t>656525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1294972</t>
+          <t>1296202</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1315723</t>
+          <t>1315819</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24364</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>37903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>621684</t>
+          <t>621113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>637990</t>
+          <t>638254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626411</t>
+          <t>628491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642862</t>
+          <t>642943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1256921</t>
+          <t>1257222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1277751</t>
+          <t>1278794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29065</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>52782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49189</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83769</t>
+          <t>81497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439474</t>
+          <t>441835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462039</t>
+          <t>461728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442184</t>
+          <t>444067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>467784</t>
+          <t>469549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>890998</t>
+          <t>893270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>925578</t>
+          <t>924949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29330</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>54982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>307357</t>
+          <t>307418</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>324243</t>
+          <t>323352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343340</t>
+          <t>340898</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361898</t>
+          <t>361416</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>658098</t>
+          <t>657110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>682762</t>
+          <t>681690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>60016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80792</t>
+          <t>80768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229230</t>
+          <t>230538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245192</t>
+          <t>245108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>341966</t>
+          <t>340153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>370034</t>
+          <t>370117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>576375</t>
+          <t>576399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611488</t>
+          <t>609154</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>80122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122688</t>
+          <t>121868</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119777</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171144</t>
+          <t>171702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>213981</t>
+          <t>211384</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>276229</t>
+          <t>277284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3271662</t>
+          <t>3272482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3313298</t>
+          <t>3314228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3373398</t>
+          <t>3372840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3424765</t>
+          <t>3422694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6662663</t>
+          <t>6661608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6724911</t>
+          <t>6727508</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para alteraciones digestivas en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44624</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375583</t>
+          <t>367343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304186</t>
+          <t>303056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668563</t>
+          <t>681759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712835</t>
+          <t>712857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>13090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411511</t>
+          <t>410457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421980</t>
+          <t>422081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498483</t>
+          <t>497948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509385</t>
+          <t>509560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915423</t>
+          <t>915604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929834</t>
+          <t>929604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>23277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35472</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517713</t>
+          <t>517975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531958</t>
+          <t>531389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519787</t>
+          <t>519191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531964</t>
+          <t>532303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1043334</t>
+          <t>1043052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1060944</t>
+          <t>1060349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59233</t>
+          <t>60157</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>41104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39559</t>
+          <t>44153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91209</t>
+          <t>93610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>828553</t>
+          <t>827629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>871918</t>
+          <t>872766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669918</t>
+          <t>671777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689132</t>
+          <t>689127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1509458</t>
+          <t>1507057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1561108</t>
+          <t>1556514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60236</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66684</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88291</t>
+          <t>86630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120497</t>
+          <t>117779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500001</t>
+          <t>500737</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>524898</t>
+          <t>524526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478203</t>
+          <t>478274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>498344</t>
+          <t>498434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>984627</t>
+          <t>987345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1016833</t>
+          <t>1018494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36445</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55508</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97618</t>
+          <t>97571</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57027</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140068</t>
+          <t>141785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>312657</t>
+          <t>313005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331720</t>
+          <t>332583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>510750</t>
+          <t>510797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>584419</t>
+          <t>583649</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>836465</t>
+          <t>834748</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>919506</t>
+          <t>920108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46858</t>
+          <t>46474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>66664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102606</t>
+          <t>103185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127847</t>
+          <t>128770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>153844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188833</t>
+          <t>186435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215305</t>
+          <t>216095</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235901</t>
+          <t>236285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>296878</t>
+          <t>295955</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>322119</t>
+          <t>321540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>518651</t>
+          <t>521049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>551472</t>
+          <t>553640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>164059</t>
+          <t>157256</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>241010</t>
+          <t>239591</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>231207</t>
+          <t>235759</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>317937</t>
+          <t>319722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>430868</t>
+          <t>428459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>543050</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3217810</t>
+          <t>3219229</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3294761</t>
+          <t>3301564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3340096</t>
+          <t>3338311</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3426826</t>
+          <t>3422274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6573803</t>
+          <t>6577651</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6685985</t>
+          <t>6688394</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A13-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>19581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485630</t>
+          <t>485751</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>450969</t>
+          <t>451620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463546</t>
+          <t>462951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>942514</t>
+          <t>941972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956138</t>
+          <t>956156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>714796</t>
+          <t>715320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>728888</t>
+          <t>729141</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>610479</t>
+          <t>611074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622536</t>
+          <t>622462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1330931</t>
+          <t>1331881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1349298</t>
+          <t>1349373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>22245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>39342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612555</t>
+          <t>613129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629180</t>
+          <t>628993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>667908</t>
+          <t>667499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682655</t>
+          <t>682755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289063</t>
+          <t>1288052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308735</t>
+          <t>1308909</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>23277</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>31117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>496463</t>
+          <t>495870</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511966</t>
+          <t>511940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484995</t>
+          <t>484525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502522</t>
+          <t>502330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>987143</t>
+          <t>986624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1010865</t>
+          <t>1011234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>23694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34417</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51762</t>
+          <t>51189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363427</t>
+          <t>363016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378080</t>
+          <t>377713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>369569</t>
+          <t>368822</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>388834</t>
+          <t>388704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>738934</t>
+          <t>739507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>763148</t>
+          <t>763321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51907</t>
+          <t>50687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270955</t>
+          <t>271076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285697</t>
+          <t>285588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306404</t>
+          <t>307079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325548</t>
+          <t>325730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>583610</t>
+          <t>584830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>608183</t>
+          <t>607783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>33898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52280</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185731</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200714</t>
+          <t>200038</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300032</t>
+          <t>300010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>319552</t>
+          <t>319621</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491511</t>
+          <t>491546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>516117</t>
+          <t>515434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>105971</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>101559</t>
+          <t>102113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142806</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>182237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237608</t>
+          <t>239500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3168704</t>
+          <t>3169554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204949</t>
+          <t>3205352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3236391</t>
+          <t>3236253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3277638</t>
+          <t>3277084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6417114</t>
+          <t>6415222</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6473583</t>
+          <t>6472485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438561</t>
+          <t>438235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>450423</t>
+          <t>450891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>419508</t>
+          <t>419672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428359</t>
+          <t>428366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863167</t>
+          <t>863674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>877094</t>
+          <t>877748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>661045</t>
+          <t>660437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>677774</t>
+          <t>677716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586746</t>
+          <t>587325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>602464</t>
+          <t>603163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1253306</t>
+          <t>1256044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1276551</t>
+          <t>1278233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>29561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54773</t>
+          <t>55859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651879</t>
+          <t>650493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669612</t>
+          <t>669552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>671835</t>
+          <t>671694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>691899</t>
+          <t>692172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1331216</t>
+          <t>1330130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1356952</t>
+          <t>1357996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45144</t>
+          <t>44684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54086</t>
+          <t>53907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88909</t>
+          <t>89909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>569473</t>
+          <t>569933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>593638</t>
+          <t>592993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561898</t>
+          <t>561949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>587460</t>
+          <t>587571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1139780</t>
+          <t>1138780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1174603</t>
+          <t>1174782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>24460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63008</t>
+          <t>63031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405272</t>
+          <t>403884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419993</t>
+          <t>419978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>400986</t>
+          <t>401404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424652</t>
+          <t>424704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>813136</t>
+          <t>813113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>840953</t>
+          <t>841553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>35807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28247</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51671</t>
+          <t>50862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47944</t>
+          <t>46403</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78176</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268785</t>
+          <t>268625</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291009</t>
+          <t>290691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302325</t>
+          <t>303134</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325749</t>
+          <t>325530</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>580252</t>
+          <t>580397</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>610484</t>
+          <t>612025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22253</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45728</t>
+          <t>43461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>29971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54140</t>
+          <t>54899</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>58236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93248</t>
+          <t>91966</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203308</t>
+          <t>205575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226783</t>
+          <t>227709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332613</t>
+          <t>331854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356789</t>
+          <t>356782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542541</t>
+          <t>543823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577257</t>
+          <t>577553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>116213</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>167490</t>
+          <t>165627</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>162886</t>
+          <t>165743</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219087</t>
+          <t>220736</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>296390</t>
+          <t>294840</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>368209</t>
+          <t>368516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3248335</t>
+          <t>3250198</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3298543</t>
+          <t>3299612</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3328023</t>
+          <t>3326374</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3384224</t>
+          <t>3381367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6594725</t>
+          <t>6594418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6666544</t>
+          <t>6668094</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408474</t>
+          <t>408721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384374</t>
+          <t>384764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394754</t>
+          <t>394753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>798213</t>
+          <t>797939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>812192</t>
+          <t>812223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571669</t>
+          <t>571927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585537</t>
+          <t>585513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>546762</t>
+          <t>547031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>558939</t>
+          <t>558995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1123863</t>
+          <t>1124588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1142077</t>
+          <t>1142475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646495</t>
+          <t>647657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662150</t>
+          <t>662240</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641993</t>
+          <t>642461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656525</t>
+          <t>655962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1296202</t>
+          <t>1295854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1315819</t>
+          <t>1315922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37903</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>621113</t>
+          <t>621958</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638254</t>
+          <t>638059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>628491</t>
+          <t>628488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642943</t>
+          <t>642978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1257222</t>
+          <t>1255643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1278794</t>
+          <t>1277765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36083</t>
+          <t>38084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>27767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52782</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49818</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81497</t>
+          <t>82075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441835</t>
+          <t>439834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>461728</t>
+          <t>462432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>444067</t>
+          <t>443920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>469549</t>
+          <t>469082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>893270</t>
+          <t>892692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>924949</t>
+          <t>925303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36864</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54982</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>307418</t>
+          <t>308864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>323352</t>
+          <t>324465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>340898</t>
+          <t>342954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>361416</t>
+          <t>362381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>657110</t>
+          <t>656436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>681690</t>
+          <t>682506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26460</t>
+          <t>27027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30052</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60016</t>
+          <t>60302</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80768</t>
+          <t>78459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230538</t>
+          <t>229971</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245108</t>
+          <t>245124</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>340153</t>
+          <t>339867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>370117</t>
+          <t>368683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>576399</t>
+          <t>578708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>609154</t>
+          <t>611648</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>82159</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121868</t>
+          <t>123631</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>119203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>171702</t>
+          <t>171138</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211384</t>
+          <t>213192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277284</t>
+          <t>277135</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3272482</t>
+          <t>3270719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3314228</t>
+          <t>3312191</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3372840</t>
+          <t>3373404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3422694</t>
+          <t>3425339</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6661608</t>
+          <t>6661757</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6727508</t>
+          <t>6725700</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>394035</t>
+          <t>403160</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367343</t>
+          <t>391175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,17 +9813,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>311568</t>
+          <t>360642</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303056</t>
+          <t>353220</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>705603</t>
+          <t>763802</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681759</t>
+          <t>752068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712857</t>
+          <t>768661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>418147</t>
+          <t>469833</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410457</t>
+          <t>461167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422081</t>
+          <t>474400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>505903</t>
+          <t>493442</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497948</t>
+          <t>486663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509560</t>
+          <t>498363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>924051</t>
+          <t>963274</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915604</t>
+          <t>953340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929604</t>
+          <t>970376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23277</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>28423</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526376</t>
+          <t>610892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517975</t>
+          <t>603474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531389</t>
+          <t>616392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>526589</t>
+          <t>603661</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519191</t>
+          <t>594977</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>532303</t>
+          <t>609732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1052965</t>
+          <t>1214553</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1043052</t>
+          <t>1204377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1060349</t>
+          <t>1222681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>58763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32138</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>44418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>70838</t>
+          <t>78561</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44153</t>
+          <t>63631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93610</t>
+          <t>95735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>4,43%</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>849086</t>
+          <t>657194</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>827629</t>
+          <t>641854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872766</t>
+          <t>668265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>680743</t>
+          <t>701748</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671777</t>
+          <t>692468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689127</t>
+          <t>710274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1529829</t>
+          <t>1358943</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507057</t>
+          <t>1341769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1556514</t>
+          <t>1373873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>93,34%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>95,57%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46698</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>61691</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>72873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>102350</t>
+          <t>109541</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86630</t>
+          <t>92862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117779</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>513539</t>
+          <t>560509</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500737</t>
+          <t>547544</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>524526</t>
+          <t>571348</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>489235</t>
+          <t>545757</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478274</t>
+          <t>534575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>498434</t>
+          <t>555346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1002774</t>
+          <t>1106266</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>987345</t>
+          <t>1089763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1018494</t>
+          <t>1122945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44897</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>58514</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>66099</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24719</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97571</t>
+          <t>78000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>106322</t>
+          <t>113286</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56425</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141785</t>
+          <t>128844</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>323268</t>
+          <t>359894</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313005</t>
+          <t>348566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332583</t>
+          <t>369382</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>546943</t>
+          <t>373067</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>510797</t>
+          <t>361166</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583649</t>
+          <t>382850</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>870211</t>
+          <t>732960</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>834748</t>
+          <t>717402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>920108</t>
+          <t>748128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>56517</t>
+          <t>60279</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46474</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66664</t>
+          <t>71180</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>114184</t>
+          <t>121802</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103185</t>
+          <t>110264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128770</t>
+          <t>136160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>170701</t>
+          <t>182080</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153844</t>
+          <t>163810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186435</t>
+          <t>199306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>226242</t>
+          <t>249919</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216095</t>
+          <t>239018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236285</t>
+          <t>260851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>310541</t>
+          <t>341608</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>295955</t>
+          <t>327250</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321540</t>
+          <t>353146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>536783</t>
+          <t>591528</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>521049</t>
+          <t>574302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>553640</t>
+          <t>609798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>220373</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157256</t>
+          <t>193771</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>239591</t>
+          <t>249185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>286511</t>
+          <t>312720</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>235759</t>
+          <t>285399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>319722</t>
+          <t>338445</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>533093</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>428459</t>
+          <t>493532</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>573701</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3250695</t>
+          <t>3311402</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3219229</t>
+          <t>3282590</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3301564</t>
+          <t>3338004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3371522</t>
+          <t>3419925</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3338311</t>
+          <t>3394200</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3422274</t>
+          <t>3447246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6622217</t>
+          <t>6731326</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6577651</t>
+          <t>6690718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6688394</t>
+          <t>6770887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
